--- a/data/trans_orig/P07B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según salud mental autopercibida en 2023</t>
+          <t>Población según salud mental autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,82 +730,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2993</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>468</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2420</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>28202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>74260</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111411</t>
+          <t>109130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84655</t>
+          <t>85617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>114261</t>
+          <t>113055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170257</t>
+          <t>168466</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>214974</t>
+          <t>214365</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134476</t>
+          <t>133581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179480</t>
+          <t>177974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143980</t>
+          <t>144708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173426</t>
+          <t>174334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288738</t>
+          <t>287003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>339796</t>
+          <t>340070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,58%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80923</t>
+          <t>84758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>29642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56532</t>
+          <t>53199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103237</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>42181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37793</t>
+          <t>39618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,47 +1575,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>54297</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>41822</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>71410</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>54297</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>40077</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>71247</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102341</t>
+          <t>100444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147529</t>
+          <t>145590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146773</t>
+          <t>149234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184732</t>
+          <t>185097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>260612</t>
+          <t>260319</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>322219</t>
+          <t>321915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>228645</t>
+          <t>230291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288965</t>
+          <t>289986</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>232190</t>
+          <t>233292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>272360</t>
+          <t>273202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>474411</t>
+          <t>474457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>545542</t>
+          <t>544803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85569</t>
+          <t>85548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137152</t>
+          <t>141030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49383</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81477</t>
+          <t>81451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144129</t>
+          <t>147830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209542</t>
+          <t>208683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>25815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37865</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>57927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59682</t>
+          <t>59254</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87658</t>
+          <t>88720</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89012</t>
+          <t>88400</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118735</t>
+          <t>116659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156113</t>
+          <t>157545</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>198612</t>
+          <t>197973</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>162843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>197374</t>
+          <t>196246</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162485</t>
+          <t>162427</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194153</t>
+          <t>194652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>333578</t>
+          <t>337129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>384473</t>
+          <t>382667</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>30065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56008</t>
+          <t>56725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>23657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>45752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58894</t>
+          <t>59086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93967</t>
+          <t>93321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>35755</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>249634</t>
+          <t>254057</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64785</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>326125</t>
+          <t>313575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84222</t>
+          <t>86572</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>125498</t>
+          <t>125974</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>71825</t>
+          <t>78830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>160619</t>
+          <t>162812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>173898</t>
+          <t>161692</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>269706</t>
+          <t>270479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80006</t>
+          <t>79052</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118484</t>
+          <t>117876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70620</t>
+          <t>74441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151161</t>
+          <t>152695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>149509</t>
+          <t>148613</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>254114</t>
+          <t>251852</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55909</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100214</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70194</t>
+          <t>71958</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>191627</t>
+          <t>196569</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>142127</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>271697</t>
+          <t>274981</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>434</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19609</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>23871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>134199</t>
+          <t>133689</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>154334</t>
+          <t>153660</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>209890</t>
+          <t>207739</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>238008</t>
+          <t>238810</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>352672</t>
+          <t>350288</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>391615</t>
+          <t>388895</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38821</t>
+          <t>38019</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>61275</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>19954</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>26029</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>45721</t>
+          <t>44925</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>31742</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>37115</t>
+          <t>37514</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>54719</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>74434</t>
+          <t>73156</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>100064</t>
+          <t>99358</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>112484</t>
+          <t>113883</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>144081</t>
+          <t>144108</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>110956</t>
+          <t>111460</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>137250</t>
+          <t>136058</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>230779</t>
+          <t>233123</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>270353</t>
+          <t>272505</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>62957</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>91373</t>
+          <t>91256</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>51734</t>
+          <t>51643</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>76001</t>
+          <t>75681</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>120279</t>
+          <t>120794</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>159261</t>
+          <t>158879</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>56020</t>
+          <t>55611</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>42370</t>
+          <t>39155</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>116955</t>
+          <t>119137</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>77998</t>
+          <t>76435</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>154937</t>
+          <t>156171</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>268606</t>
+          <t>270589</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>330206</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>400907</t>
+          <t>398778</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>665514</t>
+          <t>694796</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>696640</t>
+          <t>696315</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1064319</t>
+          <t>1049357</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>120719</t>
+          <t>117818</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>165236</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71664</t>
+          <t>66345</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>189197</t>
+          <t>191385</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>173519</t>
+          <t>176540</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>336430</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>103274</t>
+          <t>106463</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>166793</t>
+          <t>162606</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>48149</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>134029</t>
+          <t>132802</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>143241</t>
+          <t>148099</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>279113</t>
+          <t>280504</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,82 +5519,82 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>13294</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>11395</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>20053</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>6472</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>2742</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>12244</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>11395</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>5331</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>19027</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>46887</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>50950</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>73968</t>
+          <t>75193</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>58299</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>116987</t>
+          <t>116873</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>621737</t>
+          <t>620770</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>832062</t>
+          <t>829925</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>463174</t>
+          <t>460874</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>507604</t>
+          <t>505552</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1107305</t>
+          <t>1099567</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1378759</t>
+          <t>1359902</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>184592</t>
+          <t>184217</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>103394</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>138324</t>
+          <t>138598</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>144508</t>
+          <t>160705</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>300215</t>
+          <t>303076</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>81854</t>
+          <t>82052</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>59552</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>64366</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>127832</t>
+          <t>129836</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>44919</t>
+          <t>44812</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>62077</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>64166</t>
+          <t>64421</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>95653</t>
+          <t>97697</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>131886</t>
+          <t>134458</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>205529</t>
+          <t>205111</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>267857</t>
+          <t>270319</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>581291</t>
+          <t>575203</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>435856</t>
+          <t>436001</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>808837</t>
+          <t>760096</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1420385</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1994076</t>
+          <t>1985441</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1602857</t>
+          <t>1611480</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2143714</t>
+          <t>2122999</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3103999</t>
+          <t>3070897</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3852091</t>
+          <t>3837185</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>876136</t>
+          <t>864441</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1229257</t>
+          <t>1225866</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>895490</t>
+          <t>903419</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1206696</t>
+          <t>1209433</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1916420</t>
+          <t>1944617</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2383293</t>
+          <t>2398210</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>428499</t>
+          <t>428338</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>621051</t>
+          <t>616611</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>372248</t>
+          <t>368806</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>534601</t>
+          <t>542383</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>862319</t>
+          <t>846705</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1106290</t>
+          <t>1100450</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P07B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28202</t>
+          <t>28136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91753</t>
+          <t>93526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74260</t>
+          <t>77835</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109130</t>
+          <t>108008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98245</t>
+          <t>106262</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85617</t>
+          <t>92531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113055</t>
+          <t>121368</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>189997</t>
+          <t>199788</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168466</t>
+          <t>177652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>214365</t>
+          <t>221124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>156457</t>
+          <t>175982</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>133581</t>
+          <t>157488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177974</t>
+          <t>193978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>159277</t>
+          <t>178535</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144708</t>
+          <t>163350</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174334</t>
+          <t>193737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>315733</t>
+          <t>354517</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287003</t>
+          <t>329117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>340070</t>
+          <t>376913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55932</t>
+          <t>42213</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84758</t>
+          <t>60025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29642</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>75474</t>
+          <t>60582</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53199</t>
+          <t>44718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>39816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39618</t>
+          <t>40892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>55532</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41822</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>74587</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122581</t>
+          <t>124998</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100444</t>
+          <t>104709</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145590</t>
+          <t>150508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166780</t>
+          <t>175873</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149234</t>
+          <t>158030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185097</t>
+          <t>195431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>289361</t>
+          <t>300870</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>260319</t>
+          <t>272847</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321915</t>
+          <t>331269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>258846</t>
+          <t>271022</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230291</t>
+          <t>243004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289986</t>
+          <t>300677</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>251706</t>
+          <t>266439</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>233292</t>
+          <t>245622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>273202</t>
+          <t>287328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>510552</t>
+          <t>537461</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>474457</t>
+          <t>502078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>544803</t>
+          <t>573449</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>110247</t>
+          <t>108196</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85548</t>
+          <t>83691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141030</t>
+          <t>134026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>64206</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50896</t>
+          <t>55213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81451</t>
+          <t>89863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>174453</t>
+          <t>178480</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147830</t>
+          <t>149944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208683</t>
+          <t>212275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>29906</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>46307</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57927</t>
+          <t>58306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73363</t>
+          <t>72117</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59254</t>
+          <t>58625</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88720</t>
+          <t>86464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>102665</t>
+          <t>103642</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88400</t>
+          <t>90534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116659</t>
+          <t>119513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>176028</t>
+          <t>175759</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157545</t>
+          <t>157782</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>197973</t>
+          <t>195283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>180800</t>
+          <t>184445</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162843</t>
+          <t>168205</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196246</t>
+          <t>201007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>179266</t>
+          <t>184252</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162427</t>
+          <t>166531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194652</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>360065</t>
+          <t>368697</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>337129</t>
+          <t>343902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>382667</t>
+          <t>390381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>39493</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56725</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>34150</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>23742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45752</t>
+          <t>45705</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>75336</t>
+          <t>73643</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>59669</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93321</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>29957</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>103134</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35755</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>254057</t>
+          <t>48172</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>133091</t>
+          <t>69384</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65236</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>313575</t>
+          <t>89636</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>105405</t>
+          <t>114276</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86572</t>
+          <t>93377</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>125974</t>
+          <t>136950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>125694</t>
+          <t>139648</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78830</t>
+          <t>123690</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>162812</t>
+          <t>159649</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>231099</t>
+          <t>253925</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>161692</t>
+          <t>226736</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>270479</t>
+          <t>283487</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>97836</t>
+          <t>116003</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79052</t>
+          <t>96779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117876</t>
+          <t>143726</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>119029</t>
+          <t>134731</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74441</t>
+          <t>117691</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152695</t>
+          <t>153379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>216864</t>
+          <t>250734</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148613</t>
+          <t>221964</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251852</t>
+          <t>282297</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56252</t>
+          <t>81115</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102195</t>
+          <t>133147</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>116333</t>
+          <t>98108</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71958</t>
+          <t>79796</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>196569</t>
+          <t>119479</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>191224</t>
+          <t>203684</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>142127</t>
+          <t>174800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274981</t>
+          <t>239338</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>447</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,22 +3523,22 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>445</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19122</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23871</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>145211</t>
+          <t>164551</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>133689</t>
+          <t>151275</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153660</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>222331</t>
+          <t>189454</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207739</t>
+          <t>178286</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>238810</t>
+          <t>197709</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>367543</t>
+          <t>354005</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>350288</t>
+          <t>338087</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>388895</t>
+          <t>367009</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38019</t>
+          <t>46912</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>54913</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>42590</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>61275</t>
+          <t>69838</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>258234</t>
+          <t>228281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>258234</t>
+          <t>228281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>258234</t>
+          <t>228281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>436976</t>
+          <t>433946</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>436976</t>
+          <t>433946</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>436976</t>
+          <t>433946</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>36309</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>44925</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>40501</t>
+          <t>41089</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>31825</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>45747</t>
+          <t>46871</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>86249</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>73156</t>
+          <t>75496</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>99358</t>
+          <t>100829</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>128969</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>113883</t>
+          <t>115979</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>144108</t>
+          <t>146133</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,27 +4509,27 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>123059</t>
+          <t>126540</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>111460</t>
+          <t>113878</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>136058</t>
+          <t>139608</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>252028</t>
+          <t>257830</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>233123</t>
+          <t>238670</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>272505</t>
+          <t>279977</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>75613</t>
+          <t>73324</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>62957</t>
+          <t>59980</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>91256</t>
+          <t>88350</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>63550</t>
+          <t>65305</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>51643</t>
+          <t>53148</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>75681</t>
+          <t>77886</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>139163</t>
+          <t>138630</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>120794</t>
+          <t>118377</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>158879</t>
+          <t>156633</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,17 +4817,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,49 +4837,49 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>14739</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>9547</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>23245</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>13655</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>22416</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>45816</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>27449</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>55611</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>84763</t>
+          <t>97122</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>39155</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>117482</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>125280</t>
+          <t>142937</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>76435</t>
+          <t>122603</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>156171</t>
+          <t>166844</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>299845</t>
+          <t>339137</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>270589</t>
+          <t>307134</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>330206</t>
+          <t>371669</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>515812</t>
+          <t>366472</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>398778</t>
+          <t>341052</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>694796</t>
+          <t>392189</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>815657</t>
+          <t>705609</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>696315</t>
+          <t>665217</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1049357</t>
+          <t>747314</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>141533</t>
+          <t>174235</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>117818</t>
+          <t>147313</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>165236</t>
+          <t>201057</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>138900</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>66345</t>
+          <t>154140</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>191385</t>
+          <t>197119</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>280433</t>
+          <t>349509</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>176540</t>
+          <t>315883</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>336430</t>
+          <t>385668</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>131938</t>
+          <t>148461</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>106463</t>
+          <t>123442</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>162606</t>
+          <t>178426</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>96135</t>
+          <t>118451</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>100095</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>132802</t>
+          <t>138762</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>228073</t>
+          <t>266912</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>148099</t>
+          <t>234648</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>280504</t>
+          <t>302747</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,22 +5534,22 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>35072</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46887</t>
+          <t>47828</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>61808</t>
+          <t>70595</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>50950</t>
+          <t>58180</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>75193</t>
+          <t>85610</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>92630</t>
+          <t>105667</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>90263</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>116873</t>
+          <t>125399</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>709115</t>
+          <t>535484</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>620770</t>
+          <t>504927</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>829925</t>
+          <t>564874</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>485354</t>
+          <t>556702</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>460874</t>
+          <t>529575</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>505552</t>
+          <t>582558</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1194470</t>
+          <t>1092186</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1099567</t>
+          <t>1052232</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1359902</t>
+          <t>1130465</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>157021</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>57114</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>184217</t>
+          <t>186480</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>119147</t>
+          <t>141117</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>103394</t>
+          <t>121169</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>138598</t>
+          <t>161848</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>247583</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>160705</t>
+          <t>264167</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>303076</t>
+          <t>329700</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>64161</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>27649</t>
+          <t>48194</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>82052</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>54877</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>34173</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>59552</t>
+          <t>70537</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>100374</t>
+          <t>119038</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>64366</t>
+          <t>99462</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>129836</t>
+          <t>144036</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
           <t>6,1%</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>35305</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>49134</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,67 +6216,67 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>47204</t>
+          <t>51367</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>39939</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>86672</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>71889</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>105367</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>79200</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>64421</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>97697</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>172987</t>
+          <t>184721</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>134458</t>
+          <t>156476</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>205111</t>
+          <t>216912</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>350968</t>
+          <t>309428</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>270319</t>
+          <t>282405</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>575203</t>
+          <t>342480</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>523955</t>
+          <t>494149</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>436001</t>
+          <t>455203</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>760096</t>
+          <t>537155</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1587776</t>
+          <t>1485178</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1422322</t>
+          <t>1422417</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1985441</t>
+          <t>1545482</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1762628</t>
+          <t>1684924</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1611480</t>
+          <t>1632239</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2122999</t>
+          <t>1741361</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>3350404</t>
+          <t>3170102</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3070897</t>
+          <t>3087358</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3837185</t>
+          <t>3253988</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1120757</t>
+          <t>1243650</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>864441</t>
+          <t>1176790</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1225866</t>
+          <t>1300539</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1108468</t>
+          <t>1228149</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>903419</t>
+          <t>1170049</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1209433</t>
+          <t>1281728</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>2229225</t>
+          <t>2471799</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1944617</t>
+          <t>2392673</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2398210</t>
+          <t>2560562</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -6633,67 +6633,67 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>546300</t>
+          <t>583907</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>428338</t>
+          <t>529966</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>616611</t>
+          <t>641010</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>462450</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>426334</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>507400</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
           <t>12,38%</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>442467</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>368806</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>542383</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>988768</t>
+          <t>1046358</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>846705</t>
+          <t>978757</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1100450</t>
+          <t>1112471</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
